--- a/data/trans_orig/IP3109_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP3109_R-Edad-trans_orig.xlsx
@@ -768,7 +768,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>71764</t>
+          <t>71765</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>138488</t>
+          <t>138496</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2626</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>246432</t>
+          <t>245349</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>249879</t>
+          <t>249794</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>498933</t>
+          <t>498996</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4192</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3877</t>
+          <t>3962</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5447</t>
+          <t>5384</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>134541</t>
+          <t>133919</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1489,7 +1489,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>256962</t>
+          <t>256984</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>4701</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1607,7 +1607,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4451</t>
+          <t>4429</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>184206</t>
+          <t>184094</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>190191</t>
+          <t>190209</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>200516</t>
+          <t>200268</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>386577</t>
+          <t>387542</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>393166</t>
+          <t>393591</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1221</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7224</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>3241</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1930,7 +1930,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1774</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>7398</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>621017</t>
+          <t>621727</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>628319</t>
+          <t>628439</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>664625</t>
+          <t>665100</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>670309</t>
+          <t>670356</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,42 +2155,42 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>99,04%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1937</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1294077</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>1288427</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>1297908</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
           <t>98,97%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1937</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1294077</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>1289399</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1297914</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>99,4%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9283</t>
+          <t>8573</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>6454</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,47 +2268,47 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>0,96%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>7778</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>3947</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>13428</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
           <t>1,03%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>7778</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>3941</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>12456</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
         </is>
       </c>
     </row>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>260795</t>
+          <t>260045</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>496022</t>
+          <t>495297</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5542</t>
+          <t>6292</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5624</t>
+          <t>6349</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>149692</t>
+          <t>149850</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155719</t>
+          <t>155693</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>151006</t>
+          <t>151269</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>303500</t>
+          <t>304315</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>310894</t>
+          <t>311303</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>715</t>
+          <t>741</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5416</t>
+          <t>5153</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1962</t>
+          <t>1553</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9356</t>
+          <t>8541</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>156376</t>
+          <t>156422</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>165777</t>
+          <t>165672</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>169399</t>
+          <t>169639</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>175190</t>
+          <t>175232</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>328919</t>
+          <t>329647</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>339733</t>
+          <t>339735</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>4094</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>13390</t>
+          <t>13344</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>640</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6473</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>5902</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16718</t>
+          <t>15990</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,63%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>630524</t>
+          <t>630783</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>640821</t>
+          <t>641741</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>672531</t>
+          <t>673390</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>681309</t>
+          <t>681379</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1307020</t>
+          <t>1307067</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1320376</t>
+          <t>1320709</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6268</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>16306</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10824</t>
+          <t>9965</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10068</t>
+          <t>9735</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23424</t>
+          <t>23377</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>72381</t>
+          <t>71127</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>151444</t>
+          <t>150995</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4780,7 +4780,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3043</t>
+          <t>4297</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4795,7 +4795,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4815,7 +4815,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4830,7 +4830,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>173048</t>
+          <t>172578</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>179332</t>
+          <t>179454</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>357416</t>
+          <t>357381</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>363806</t>
+          <t>363814</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1365</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7649</t>
+          <t>8119</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1324</t>
+          <t>1316</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7714</t>
+          <t>7749</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>161772</t>
+          <t>161387</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>168874</t>
+          <t>168873</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>162524</t>
+          <t>162133</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>168202</t>
+          <t>168204</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>326608</t>
+          <t>327406</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>335644</t>
+          <t>336243</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2353</t>
+          <t>2354</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9455</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>710</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>6781</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4498</t>
+          <t>3899</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13534</t>
+          <t>12736</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,74%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>623141</t>
+          <t>623967</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>633248</t>
+          <t>633158</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>671670</t>
+          <t>671595</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>678192</t>
+          <t>678189</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,7 +6049,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1298837</t>
+          <t>1298866</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1310327</t>
+          <t>1310047</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,42%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4992</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15009</t>
+          <t>14183</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7852</t>
+          <t>7927</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>7625</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18835</t>
+          <t>18806</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>34127</t>
+          <t>34539</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42564</t>
+          <t>42235</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33282</t>
+          <t>33556</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41070</t>
+          <t>41196</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,5%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71366</t>
+          <t>71173</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81520</t>
+          <t>81659</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,97%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>4260</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12368</t>
+          <t>11956</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12003</t>
+          <t>11729</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10259</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20413</t>
+          <t>20606</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,45%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>132809</t>
+          <t>132369</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>145979</t>
+          <t>146415</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>143296</t>
+          <t>143710</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>160320</t>
+          <t>160333</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>280914</t>
+          <t>279575</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>303289</t>
+          <t>301565</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>81,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,37%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13320</t>
+          <t>12884</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26490</t>
+          <t>26930</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21639</t>
+          <t>21626</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38663</t>
+          <t>38249</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,25%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>37970</t>
+          <t>39694</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>60345</t>
+          <t>61684</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,08%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>142971</t>
+          <t>142547</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>158474</t>
+          <t>157609</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>164939</t>
+          <t>163356</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>184461</t>
+          <t>184603</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>311502</t>
+          <t>309690</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>336002</t>
+          <t>337372</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,63%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14598</t>
+          <t>15463</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30101</t>
+          <t>30525</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27464</t>
+          <t>27322</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>46986</t>
+          <t>48569</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>48996</t>
+          <t>47626</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73496</t>
+          <t>75308</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>219805</t>
+          <t>220115</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>244859</t>
+          <t>244463</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>80,38%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>254472</t>
+          <t>253560</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>276922</t>
+          <t>276737</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>480940</t>
+          <t>479887</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>514504</t>
+          <t>515208</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>82,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>89,07%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28584</t>
+          <t>28980</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>53638</t>
+          <t>53328</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28077</t>
+          <t>28262</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50527</t>
+          <t>51439</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>63938</t>
+          <t>63234</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>97502</t>
+          <t>98555</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>17,04%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>546448</t>
+          <t>546713</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>578200</t>
+          <t>578076</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>610647</t>
+          <t>612287</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>648538</t>
+          <t>648671</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1167812</t>
+          <t>1170793</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1216947</t>
+          <t>1216566</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,12%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>74109</t>
+          <t>74233</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>105861</t>
+          <t>105596</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95631</t>
+          <t>95498</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>133522</t>
+          <t>131882</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>179531</t>
+          <t>179912</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>228666</t>
+          <t>225685</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP3109_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP3109_R-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,74 +723,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>75021</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>72430</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>75669</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>99,14%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>95,72%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>65453</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>75021</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>71765</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>75669</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>94,84%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>212</t>
@@ -803,7 +803,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>138496</t>
+          <t>137853</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -836,107 +836,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3239</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4,28%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>648</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>3904</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>3269</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>5,16%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>2626</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>75669</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>75669</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>75669</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>65453</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>65453</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>65453</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>75669</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>75669</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>75669</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,107 +1066,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>253107</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>250521</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>99,74%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>98,73%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>373</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>249271</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>245349</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>245907</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>250624</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>99,46%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>97,9%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>98,12%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>253107</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>249794</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>98,44%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>502378</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>499010</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>504380</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>98,94%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>754</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>502378</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>498996</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>503740</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>98,93%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>99,87%</t>
         </is>
       </c>
     </row>
@@ -1179,107 +1179,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3235</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1353</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5275</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4717</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,54%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>649</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>1,88%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3962</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>5370</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>5384</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>375</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>250624</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>250624</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>250624</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,74 +1409,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>137325</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>134592</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>138620</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>99,07%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>97,09%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>122793</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>137325</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>133919</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>138620</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>99,07%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>96,61%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>389</t>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>256984</t>
+          <t>256822</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1522,107 +1522,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4028</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,91%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="R11" s="2" t="inlineStr">
         <is>
           <t>1295</t>
         </is>
       </c>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>4701</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>4591</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>0,5%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>1295</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>4429</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>138620</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>138620</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>138620</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>184</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>122793</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>122793</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>122793</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>138620</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>138620</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>138620</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>202912</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>200407</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>203509</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>98,48%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>188194</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>184094</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>190209</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>184720</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>190243</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>98,31%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>96,17%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>305</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>202912</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>200268</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>203509</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>387542</t>
+          <t>386980</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3102</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>3236</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1221</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7336</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1187</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6710</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>1,69%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3241</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7398</t>
+          <t>7960</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>203509</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>203509</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>203509</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>282</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>191430</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>191430</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>191430</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>203509</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>203509</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>203509</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,74 +2095,74 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1004</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>668364</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>663978</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>670307</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>98,87%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>99,81%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>933</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>625712</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>621727</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>628439</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>621572</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>628395</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>99,27%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>98,64%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>98,62%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>99,7%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>1004</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>668364</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>665100</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>670356</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>99,52%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>99,04%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1937</t>
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1288427</t>
+          <t>1288767</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1297908</t>
+          <t>1297479</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,7%</t>
+          <t>99,66%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3190</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1247</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>7576</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>4588</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1861</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>8573</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1905</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>8728</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>0,73%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3190</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1198</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>6454</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3947</t>
+          <t>4376</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13428</t>
+          <t>13088</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1009</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>671554</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>671554</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>671554</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>940</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>630300</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>630300</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>630300</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1009</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>671554</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>671554</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>671554</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,47 +2670,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>84724</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>85580</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>84724</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>84724</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>84724</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>84724</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>131</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>85580</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>85580</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>85580</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>84724</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>84724</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>84724</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,74 +3013,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>265209</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>260328</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>266337</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>99,58%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>97,74%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>338</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>235309</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>265209</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>260045</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>266337</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>99,58%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>97,64%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>707</t>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>495297</t>
+          <t>495318</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -3126,107 +3126,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1128</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>6009</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>1128</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>6292</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>6328</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1128</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>6349</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>266337</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>266337</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>266337</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>338</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>235309</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>235309</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>235309</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>266337</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>266337</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>266337</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,74 +3356,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>154970</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>151910</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>156422</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>99,07%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>97,12%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>153606</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>149850</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>155693</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>149270</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>155696</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>98,19%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>95,79%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>95,42%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>99,53%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>154970</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>151269</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>156422</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>99,07%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>96,71%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>441</t>
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>304315</t>
+          <t>304147</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>311303</t>
+          <t>311344</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,52%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1452</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4512</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>2828</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>6584</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>738</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>7164</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>1,81%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>0,47%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1452</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>5153</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1553</t>
+          <t>1512</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>8541</t>
+          <t>8709</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>156422</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>156422</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>156422</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>156434</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>156434</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>156434</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>156422</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>156422</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>156422</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>173308</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>169643</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>175198</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>98,54%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>96,46%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>99,62%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>162227</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>156422</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>165672</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>156107</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>165724</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>95,56%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>92,14%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>97,59%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>173308</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>169639</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>175232</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>98,54%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>329647</t>
+          <t>329138</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>339735</t>
+          <t>339751</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2564</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6229</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>7539</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>4094</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>13344</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>4042</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>13659</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>4,44%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>7,86%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2564</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>640</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>6233</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5902</t>
+          <t>5886</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15990</t>
+          <t>16499</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>175872</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>175872</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>175872</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>169766</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>169766</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>169766</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>175872</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>175872</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>175872</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>678211</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>672601</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>681256</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>99,25%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>98,43%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>99,69%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>917</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>636722</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>630783</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>641741</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>630203</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>641399</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>98,4%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>97,48%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>99,17%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>678211</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>673390</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>681379</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>99,25%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1307067</t>
+          <t>1307488</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1320709</t>
+          <t>1320651</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>5144</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2099</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>10754</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>10367</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>5348</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>16306</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>5690</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>16886</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>1,6%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>5144</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>9965</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9735</t>
+          <t>9793</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23377</t>
+          <t>22956</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>683355</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>683355</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>683355</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>932</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>647089</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>647089</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>647089</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>683355</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>683355</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>683355</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,74 +4617,74 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>74709</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>71842</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>75424</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>95,25%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>79611</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>74709</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>71127</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>75424</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>99,05%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>94,3%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>241</t>
@@ -4697,7 +4697,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>150995</t>
+          <t>151480</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4730,107 +4730,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>715</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>3582</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>4,75%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>715</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>4297</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>3555</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>715</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>4040</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>75424</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>75424</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>75424</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>128</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>79611</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>79611</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>79611</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>75424</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>75424</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>75424</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,47 +4960,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>250750</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>325</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>206615</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>250750</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>369</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>250750</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>250750</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>250750</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>325</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>206615</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>206615</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>206615</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>250750</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>250750</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>250750</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>184433</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>255</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>176945</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>172578</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>179454</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>173090</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>179438</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>97,92%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>95,51%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>99,31%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>184433</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>357381</t>
+          <t>356720</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>363814</t>
+          <t>363762</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>3752</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>1243</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>8119</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1259</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>7607</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>2,08%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>4,49%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1316</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7749</t>
+          <t>8410</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>184433</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>184433</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>184433</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>180697</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>180697</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>180697</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>257</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>184433</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>184433</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>184433</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>166123</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>162517</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>168200</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>98,35%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>96,21%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>99,58%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>166160</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>161387</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>168873</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>161885</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>168908</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>97,04%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>94,25%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>98,63%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>166123</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>162133</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>168204</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>98,35%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>327406</t>
+          <t>326400</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>336243</t>
+          <t>335885</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2791</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>714</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6397</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,65%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3,79%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>5067</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2354</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>9840</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2319</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>9342</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>2,96%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5,75%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2791</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>710</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>6781</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>4257</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>12736</t>
+          <t>13742</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>168914</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>168914</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>168914</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>171227</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>171227</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>171227</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>168914</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>168914</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>168914</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>963</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>676016</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>671818</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>678182</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>98,87%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>99,8%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>943</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>629330</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>623967</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>633158</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>623491</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>633072</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>98,62%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>97,78%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>99,22%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>963</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>676016</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>671595</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>678189</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1298866</t>
+          <t>1298718</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1310047</t>
+          <t>1309896</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3506</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>7704</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>8820</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>4992</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>14183</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>5078</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>14659</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>1,38%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3506</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>1333</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>7927</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7625</t>
+          <t>7776</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18806</t>
+          <t>18954</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>968</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>679522</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>679522</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>679522</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>957</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>638150</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>638150</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>638150</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>968</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>679522</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>679522</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>679522</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>31839</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>28427</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>34128</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>85,05%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>75,94%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>91,17%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>39151</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>34539</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>42235</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>84,21%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>74,29%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>90,84%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>37976</t>
+          <t>36250</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33556</t>
+          <t>32324</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41196</t>
+          <t>39344</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>77126</t>
+          <t>68089</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>71173</t>
+          <t>62868</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81659</t>
+          <t>72074</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>77,55%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,96%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>5596</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3307</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>9008</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>14,95%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>8,83%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>24,06%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>7344</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4260</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11956</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>15,79%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>9,16%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>25,71%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>6431</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>3337</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11729</t>
+          <t>10357</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>14653</t>
+          <t>12027</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10120</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20606</t>
+          <t>17248</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>132674</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>124972</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>139360</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>84,48%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>79,58%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>88,74%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>139995</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>132369</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>146415</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>87,88%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>83,09%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>91,91%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>152238</t>
+          <t>127456</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>143710</t>
+          <t>120795</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>160333</t>
+          <t>132278</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>78,98%</t>
+          <t>83,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>292234</t>
+          <t>260130</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>279575</t>
+          <t>249969</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>301565</t>
+          <t>269967</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>89,23%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>24368</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17682</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>32070</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>15,52%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>11,26%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>20,42%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>19304</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>12884</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>26930</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>12,12%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>8,09%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>16,91%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>29721</t>
+          <t>18062</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21626</t>
+          <t>13240</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>38249</t>
+          <t>24723</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>49025</t>
+          <t>42430</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39694</t>
+          <t>32593</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61684</t>
+          <t>52591</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>165865</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>156600</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>175035</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>83,09%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>78,45%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>87,69%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>151000</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>142547</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>157609</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>87,25%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>82,36%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>91,07%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>174642</t>
+          <t>152127</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>163356</t>
+          <t>144156</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>184603</t>
+          <t>159435</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>82,41%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>325643</t>
+          <t>317992</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>309690</t>
+          <t>305101</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>337372</t>
+          <t>328942</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,89%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>33749</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>24579</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>43014</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>16,91%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>12,31%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>21,55%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>22072</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>15463</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>30525</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>12,75%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>8,93%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>17,64%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>37283</t>
+          <t>22545</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27322</t>
+          <t>15237</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48569</t>
+          <t>30516</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>59355</t>
+          <t>56294</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47626</t>
+          <t>45344</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>75308</t>
+          <t>69185</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>199614</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>199614</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>199614</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>211925</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>211925</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>211925</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>384998</t>
+          <t>374286</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>384998</t>
+          <t>374286</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>384998</t>
+          <t>374286</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>256770</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>245802</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>266404</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>87,87%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>84,12%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>91,17%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>281</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>232543</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>220115</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>244463</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>85,04%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>80,5%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>89,4%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>266320</t>
+          <t>211666</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>253560</t>
+          <t>200400</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>276737</t>
+          <t>221521</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>498863</t>
+          <t>468436</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>479887</t>
+          <t>451654</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>515208</t>
+          <t>481600</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>88,09%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>35451</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>25817</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>46419</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>12,13%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8,83%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>15,88%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>40900</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>28980</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>53328</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>14,96%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>10,6%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>19,5%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>38679</t>
+          <t>42797</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28262</t>
+          <t>32942</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>51439</t>
+          <t>54063</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>79579</t>
+          <t>78248</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>63234</t>
+          <t>65084</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>98555</t>
+          <t>95030</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>292221</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>292221</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>292221</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>273443</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>273443</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>273443</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>254463</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>254463</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>254463</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>578442</t>
+          <t>546684</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>578442</t>
+          <t>546684</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>578442</t>
+          <t>546684</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>783</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>587149</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>573183</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>602201</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>85,55%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>83,52%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>87,74%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>779</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>562689</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>546713</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>578076</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>86,26%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>83,81%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>88,62%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>631176</t>
+          <t>527499</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>612287</t>
+          <t>510168</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>648671</t>
+          <t>540931</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1193865</t>
+          <t>1114648</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1170793</t>
+          <t>1091553</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1216566</t>
+          <t>1133237</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>86,93%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>99163</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>84111</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>113129</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>14,45%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>12,26%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>16,48%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>89620</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>74233</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>105596</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>13,74%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>11,38%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>16,19%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>112993</t>
+          <t>89835</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95498</t>
+          <t>76403</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>131882</t>
+          <t>107166</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>202613</t>
+          <t>188998</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>179912</t>
+          <t>170409</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>225685</t>
+          <t>212093</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,5%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686312</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686312</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686312</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>652309</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>652309</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>652309</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744169</t>
+          <t>617334</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744169</t>
+          <t>617334</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744169</t>
+          <t>617334</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1396478</t>
+          <t>1303646</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1396478</t>
+          <t>1303646</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1396478</t>
+          <t>1303646</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
